--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1212,6 +1212,242 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132469510</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Naturreservat Mörkedal , Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564727</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6465332</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Den skiktade och olikåldriga samt fuktiga tallskogen av skvattramtyp som hänger i hopp med det befintliga naturreservatet Mörkedal verkar vara en viktig del i talltitans revir och livsmiljö.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132469468</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Naturreservat Mörkedal , Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564730</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6465383</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Verkar som att hönan letade ställe för att häcka respektive lägga ägg.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132458340</v>
       </c>
       <c r="B2" t="n">
-        <v>57127</v>
+        <v>57128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132458329</v>
       </c>
       <c r="B3" t="n">
-        <v>57253</v>
+        <v>57254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132458326</v>
       </c>
       <c r="B4" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>132458325</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>132469510</v>
       </c>
       <c r="B7" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>132469468</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132458340</v>
       </c>
       <c r="B2" t="n">
-        <v>57128</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132458329</v>
       </c>
       <c r="B3" t="n">
-        <v>57254</v>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132458326</v>
       </c>
       <c r="B4" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>132458325</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>132469510</v>
       </c>
       <c r="B7" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>132469468</v>
       </c>
       <c r="B8" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132458340</v>
       </c>
       <c r="B2" t="n">
-        <v>57132</v>
+        <v>57133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>132458329</v>
       </c>
       <c r="B3" t="n">
-        <v>57258</v>
+        <v>57259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132458326</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>132458325</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>132469510</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>132469468</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>132458326</v>
       </c>
       <c r="B4" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132458340</v>
+        <v>132458326</v>
       </c>
       <c r="B2" t="n">
-        <v>57136</v>
+        <v>79992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564659</v>
+        <v>564805</v>
       </c>
       <c r="R2" t="n">
-        <v>6465432</v>
+        <v>6465345</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132458329</v>
+        <v>132458325</v>
       </c>
       <c r="B3" t="n">
-        <v>57263</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,16 +787,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,14 +806,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564805</v>
+        <v>564785</v>
       </c>
       <c r="R3" t="n">
-        <v>6465345</v>
+        <v>6465364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,37 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132458326</v>
+        <v>132458329</v>
       </c>
       <c r="B4" t="n">
-        <v>79952</v>
+        <v>57280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -975,7 +984,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,38 +1002,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132458321</v>
+        <v>132469468</v>
       </c>
       <c r="B5" t="n">
-        <v>5495</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1034,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564763</v>
+        <v>564730</v>
       </c>
       <c r="R5" t="n">
-        <v>6465344</v>
+        <v>6465383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,12 +1083,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Verkar som att hönan letade ställe för att häcka respektive lägga ägg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1097,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132458325</v>
+        <v>132458321</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>5497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,43 +1131,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564785</v>
+        <v>564763</v>
       </c>
       <c r="R6" t="n">
-        <v>6465364</v>
+        <v>6465344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1204,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1214,44 +1223,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132469510</v>
+        <v>132458340</v>
       </c>
       <c r="B7" t="n">
-        <v>58119</v>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1265,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564727</v>
+        <v>564659</v>
       </c>
       <c r="R7" t="n">
-        <v>6465332</v>
+        <v>6465432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,17 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Den skiktade och olikåldriga samt fuktiga tallskogen av skvattramtyp som hänger i hopp med det befintliga naturreservatet Mörkedal verkar vara en viktig del i talltitans revir och livsmiljö.</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,32 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132469468</v>
+        <v>132458335</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,12 +1370,12 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564730</v>
+        <v>564796</v>
       </c>
       <c r="R8" t="n">
-        <v>6465383</v>
+        <v>6465386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,17 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Verkar som att hönan letade ställe för att häcka respektive lägga ägg.</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,6 +1442,233 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132469510</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Naturreservat Mörkedal , Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564727</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6465332</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Den skiktade och olikåldriga samt fuktiga tallskogen av skvattramtyp som hänger i hopp med det befintliga naturreservatet Mörkedal verkar vara en viktig del i talltitans revir och livsmiljö.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132458344</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Naturreservat Mörkedal , Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564737</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6465336</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12068-2026 artfynd.xlsx
+++ b/artfynd/A 12068-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458326</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458325</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458321</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458340</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458335</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132469510</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,8 +1714,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458344</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>